--- a/data/trans_dic/P34B04_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P34B04_R-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza algún entrenamiento físico deportivo, como fútbol, baloncesto, ciclismo, natación de competición, judo, kárate o similares, 3 veces por semana o más</t>
+          <t>Población que realiza algún entrenamiento físico deportivo, como fútbol, baloncesto, ciclismo, natación de competición, judo, kárate o similares, durante más de 30 minutos, 3 veces por semana o más (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,03; 14,01</t>
+          <t>8,33; 14,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,4; 8,09</t>
+          <t>3,22; 7,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,69; 15,95</t>
+          <t>8,71; 15,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 5,3</t>
+          <t>1,12; 6,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,08</t>
+          <t>0,53; 3,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,51</t>
+          <t>2,12; 5,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,83; 9,88</t>
+          <t>5,85; 10,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,35; 5,1</t>
+          <t>2,36; 5,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,17; 10,72</t>
+          <t>6,17; 10,35</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,27; 9,55</t>
+          <t>4,1; 9,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,33; 8,46</t>
+          <t>3,48; 8,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,65; 13,72</t>
+          <t>6,38; 13,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,26</t>
+          <t>0,82; 3,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,27</t>
+          <t>0,84; 3,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 5,46</t>
+          <t>2,28; 5,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,57; 5,43</t>
+          <t>2,66; 5,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,41; 8,43</t>
+          <t>4,19; 8,12</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 7,22</t>
+          <t>3,65; 7,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,69</t>
+          <t>1,84; 4,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 6,57</t>
+          <t>1,21; 6,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,13</t>
+          <t>0,35; 3,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,67</t>
+          <t>0,0; 3,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 7,07</t>
+          <t>1,52; 7,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,71; 5,43</t>
+          <t>2,77; 5,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,03</t>
+          <t>1,59; 3,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 5,88</t>
+          <t>1,41; 5,82</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,95; 6,67</t>
+          <t>3,93; 6,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,44; 7,36</t>
+          <t>4,48; 7,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,05; 7,98</t>
+          <t>4,05; 8,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,78</t>
+          <t>0,35; 1,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,32</t>
+          <t>0,8; 2,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,49</t>
+          <t>0,63; 2,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,67; 4,4</t>
+          <t>2,69; 4,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,13; 4,85</t>
+          <t>3,03; 4,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,96</t>
+          <t>2,45; 4,98</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,98; 7,95</t>
+          <t>3,87; 7,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,12; 6,7</t>
+          <t>3,16; 6,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,7; 9,36</t>
+          <t>3,81; 9,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,8</t>
+          <t>0,0; 0,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,23</t>
+          <t>0,13; 1,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,02</t>
+          <t>0,21; 1,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,34</t>
+          <t>1,64; 3,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 3,51</t>
+          <t>1,7; 3,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,76</t>
+          <t>1,57; 3,75</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16,7; 27,03</t>
+          <t>17,1; 27,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16,03; 25,88</t>
+          <t>15,87; 25,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19,49; 38,35</t>
+          <t>19,44; 38,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,49</t>
+          <t>0,35; 1,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,15</t>
+          <t>0,71; 2,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,81</t>
+          <t>0,7; 2,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,79; 6,03</t>
+          <t>3,79; 6,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,33; 6,81</t>
+          <t>4,36; 6,72</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,54; 10,69</t>
+          <t>5,74; 10,98</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,57; 8,35</t>
+          <t>6,52; 8,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,48; 7,2</t>
+          <t>5,4; 7,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,66; 9,85</t>
+          <t>6,6; 9,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,16</t>
+          <t>0,5; 1,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,64</t>
+          <t>0,92; 1,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,12</t>
+          <t>1,16; 2,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,57; 4,56</t>
+          <t>3,58; 4,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,25; 4,15</t>
+          <t>3,31; 4,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,06; 5,66</t>
+          <t>4,03; 5,64</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza algún entrenamiento físico deportivo, como fútbol, baloncesto, ciclismo, natación de competición, judo, kárate o similares, 3 veces por semana o más</t>
+          <t>Población que realiza algún entrenamiento físico deportivo, como fútbol, baloncesto, ciclismo, natación de competición, judo, kárate o similares, durante más de 30 minutos, 3 veces por semana o más (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>35107; 61237</t>
+          <t>36406; 63599</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14604; 34704</t>
+          <t>13815; 32996</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43922; 80567</t>
+          <t>44001; 78673</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3437; 16654</t>
+          <t>3513; 20260</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1849; 10695</t>
+          <t>1848; 10657</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10352; 24646</t>
+          <t>9464; 24098</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43806; 74236</t>
+          <t>43962; 75131</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18232; 39601</t>
+          <t>18290; 39024</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58740; 102155</t>
+          <t>58756; 98608</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17883; 40013</t>
+          <t>17176; 39742</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12574; 31922</t>
+          <t>13126; 30953</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30094; 62023</t>
+          <t>28834; 59721</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2120</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3848; 15869</t>
+          <t>3064; 14438</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2618; 12431</t>
+          <t>3183; 13180</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17944; 41303</t>
+          <t>17226; 40090</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19232; 40672</t>
+          <t>19924; 39831</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36714; 70198</t>
+          <t>34888; 67594</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>22378; 45406</t>
+          <t>22972; 44391</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9711; 24456</t>
+          <t>9608; 25074</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7069; 43919</t>
+          <t>8068; 45118</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>896; 8132</t>
+          <t>902; 8117</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6102</t>
+          <t>0; 6549</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2438; 11797</t>
+          <t>2538; 12443</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24068; 48282</t>
+          <t>24590; 48766</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10793; 27732</t>
+          <t>10948; 27324</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11808; 49103</t>
+          <t>11808; 48576</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>45739; 77359</t>
+          <t>45547; 76474</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>51032; 84631</t>
+          <t>51513; 84386</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41950; 82576</t>
+          <t>41906; 83830</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1970; 13634</t>
+          <t>2695; 13861</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6518; 19141</t>
+          <t>6640; 20292</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6094; 24329</t>
+          <t>6172; 23886</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>51274; 84684</t>
+          <t>51792; 85250</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>61826; 95838</t>
+          <t>59821; 95206</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>48766; 99879</t>
+          <t>49261; 100288</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>20300; 40595</t>
+          <t>19760; 40545</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19340; 41597</t>
+          <t>19640; 41981</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17543; 44371</t>
+          <t>18068; 45969</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 6073</t>
+          <t>0; 5713</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>963; 9050</t>
+          <t>971; 9862</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1665; 8541</t>
+          <t>1743; 9560</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20122; 42465</t>
+          <t>20914; 41920</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>23162; 47657</t>
+          <t>23083; 46897</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>20750; 49372</t>
+          <t>20601; 49203</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>44376; 71822</t>
+          <t>45450; 72036</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>46019; 74315</t>
+          <t>45560; 73523</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>46881; 92235</t>
+          <t>46745; 93198</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4738; 16561</t>
+          <t>3915; 16426</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8553; 23291</t>
+          <t>7701; 22514</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5173; 21353</t>
+          <t>5291; 22205</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>52063; 82934</t>
+          <t>52139; 83201</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>59287; 93226</t>
+          <t>59724; 91984</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>55440; 106920</t>
+          <t>57461; 109822</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>224725; 285473</t>
+          <t>222972; 286804</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>185489; 243866</t>
+          <t>182821; 242014</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>224718; 332583</t>
+          <t>222739; 332470</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18465; 40989</t>
+          <t>17878; 39730</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>33566; 57817</t>
+          <t>32587; 59013</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>42229; 75700</t>
+          <t>41588; 73681</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>249082; 317990</t>
+          <t>249500; 317933</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>224966; 287189</t>
+          <t>228627; 291885</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>281919; 392907</t>
+          <t>279815; 391638</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P34B04_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P34B04_R-Clase-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,33; 14,55</t>
+          <t>8,5; 14,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,22; 7,69</t>
+          <t>3,42; 7,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,71; 15,57</t>
+          <t>8,7; 15,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 6,44</t>
+          <t>1,11; 6,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,07</t>
+          <t>0,54; 3,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,39</t>
+          <t>2,23; 5,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,85; 10,0</t>
+          <t>5,6; 9,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,36; 5,03</t>
+          <t>2,46; 5,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,17; 10,35</t>
+          <t>6,08; 9,96</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -788,17 +788,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,1; 9,49</t>
+          <t>4,03; 9,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,48; 8,21</t>
+          <t>3,4; 8,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,38; 13,21</t>
+          <t>6,36; 12,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -808,27 +808,27 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,88</t>
+          <t>1,04; 4,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,46</t>
+          <t>0,67; 3,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,3</t>
+          <t>2,24; 5,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,66; 5,31</t>
+          <t>2,56; 5,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 8,12</t>
+          <t>3,98; 7,47</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,65; 7,06</t>
+          <t>3,59; 7,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,8</t>
+          <t>1,82; 4,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 6,75</t>
+          <t>4,04; 9,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,12</t>
+          <t>0,35; 3,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,94</t>
+          <t>0,0; 3,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 7,45</t>
+          <t>1,46; 6,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,77; 5,49</t>
+          <t>2,81; 5,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,97</t>
+          <t>1,65; 4,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 5,82</t>
+          <t>3,77; 7,81</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -1008,17 +1008,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,93; 6,6</t>
+          <t>4,03; 6,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,48; 7,34</t>
+          <t>4,32; 7,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,05; 8,1</t>
+          <t>3,9; 7,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1028,27 +1028,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,46</t>
+          <t>0,78; 2,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,44</t>
+          <t>1,03; 3,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,69; 4,43</t>
+          <t>2,66; 4,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,03; 4,82</t>
+          <t>3,12; 4,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 4,98</t>
+          <t>2,96; 5,1</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,87; 7,94</t>
+          <t>3,92; 7,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,16; 6,76</t>
+          <t>3,14; 6,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,81; 9,7</t>
+          <t>4,06; 10,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,75</t>
+          <t>0,0; 0,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,34</t>
+          <t>0,14; 1,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,14</t>
+          <t>0,24; 1,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,3</t>
+          <t>1,59; 3,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 3,45</t>
+          <t>1,72; 3,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,75</t>
+          <t>1,99; 4,56</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,1; 27,11</t>
+          <t>16,5; 26,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15,87; 25,6</t>
+          <t>16,28; 25,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19,44; 38,75</t>
+          <t>21,31; 39,79</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,48</t>
+          <t>0,43; 1,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,08</t>
+          <t>0,79; 2,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,92</t>
+          <t>0,81; 3,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,79; 6,05</t>
+          <t>3,73; 6,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,36; 6,72</t>
+          <t>4,21; 6,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,74; 10,98</t>
+          <t>5,51; 10,24</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,52; 8,39</t>
+          <t>6,55; 8,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,4; 7,15</t>
+          <t>5,48; 7,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,6; 9,85</t>
+          <t>7,74; 10,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,12</t>
+          <t>0,5; 1,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,92; 1,67</t>
+          <t>0,97; 1,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,06</t>
+          <t>1,39; 2,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,58; 4,56</t>
+          <t>3,62; 4,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,31; 4,22</t>
+          <t>3,28; 4,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,03; 5,64</t>
+          <t>4,6; 5,94</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59869</t>
+          <t>64445</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15712</t>
+          <t>16486</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>75581</t>
+          <t>80930</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>36406; 63599</t>
+          <t>37183; 62461</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13815; 32996</t>
+          <t>14662; 33489</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44001; 78673</t>
+          <t>47883; 84437</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3513; 20260</t>
+          <t>3482; 19803</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1848; 10657</t>
+          <t>1860; 11161</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9464; 24098</t>
+          <t>10885; 25120</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43962; 75131</t>
+          <t>42098; 72936</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18290; 39024</t>
+          <t>19083; 39958</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58756; 98608</t>
+          <t>63172; 103512</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43077</t>
+          <t>44167</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>6630</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>49380</t>
+          <t>50797</t>
         </is>
       </c>
     </row>
@@ -1802,17 +1802,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17176; 39742</t>
+          <t>16864; 39230</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13126; 30953</t>
+          <t>12834; 31701</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28834; 59721</t>
+          <t>30751; 60422</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1822,27 +1822,27 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3064; 14438</t>
+          <t>3854; 15796</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3183; 13180</t>
+          <t>2830; 13491</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17226; 40090</t>
+          <t>16950; 41027</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19924; 39831</t>
+          <t>19184; 41536</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34888; 67594</t>
+          <t>35988; 67564</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>29901</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5930</t>
+          <t>6353</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30615</t>
+          <t>36254</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>22972; 44391</t>
+          <t>22546; 45073</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9608; 25074</t>
+          <t>9524; 24204</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8068; 45118</t>
+          <t>19057; 44898</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>902; 8117</t>
+          <t>905; 8069</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6549</t>
+          <t>0; 6171</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2538; 12443</t>
+          <t>2730; 12644</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24590; 48766</t>
+          <t>25000; 47031</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10948; 27324</t>
+          <t>11353; 28064</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11808; 48576</t>
+          <t>24817; 51461</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58520</t>
+          <t>62504</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13874</t>
+          <t>15445</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>72395</t>
+          <t>77950</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>45547; 76474</t>
+          <t>46715; 78135</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>51513; 84386</t>
+          <t>49614; 82401</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41906; 83830</t>
+          <t>44088; 82881</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2695; 13861</t>
+          <t>2682; 13873</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6640; 20292</t>
+          <t>6461; 19802</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6172; 23886</t>
+          <t>8854; 26202</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>51792; 85250</t>
+          <t>51162; 84103</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>59821; 95206</t>
+          <t>61557; 97863</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>49261; 100288</t>
+          <t>59018; 101490</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28045</t>
+          <t>36800</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>4664</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>32101</t>
+          <t>41464</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>19760; 40545</t>
+          <t>20016; 40740</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19640; 41981</t>
+          <t>19461; 42172</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18068; 45969</t>
+          <t>22993; 58883</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 5713</t>
+          <t>0; 5297</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>971; 9862</t>
+          <t>1042; 10129</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1743; 9560</t>
+          <t>1951; 9332</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20914; 41920</t>
+          <t>20235; 41667</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>23083; 46897</t>
+          <t>23324; 45785</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>20601; 49203</t>
+          <t>27779; 63743</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>67630</t>
+          <t>69461</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11358</t>
+          <t>14276</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>78988</t>
+          <t>83737</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>45450; 72036</t>
+          <t>43848; 70514</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>45560; 73523</t>
+          <t>46735; 73495</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>46745; 93198</t>
+          <t>50547; 94398</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3915; 16426</t>
+          <t>4750; 16463</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7701; 22514</t>
+          <t>8497; 23009</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5291; 22205</t>
+          <t>6792; 27248</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>52139; 83201</t>
+          <t>51328; 82848</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>59724; 91984</t>
+          <t>57705; 91708</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>57461; 109822</t>
+          <t>59468; 110538</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>281827</t>
+          <t>307278</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>57233</t>
+          <t>63854</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>339060</t>
+          <t>371132</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>222972; 286804</t>
+          <t>223952; 285479</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>182821; 242014</t>
+          <t>185695; 243675</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>222739; 332470</t>
+          <t>266395; 356644</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17878; 39730</t>
+          <t>17867; 41322</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>32587; 59013</t>
+          <t>34148; 58979</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>41588; 73681</t>
+          <t>50302; 82008</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>249500; 317933</t>
+          <t>252164; 319326</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>228627; 291885</t>
+          <t>227158; 290064</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>279815; 391638</t>
+          <t>325132; 420185</t>
         </is>
       </c>
     </row>
